--- a/artfynd/A 50854-2022 artfynd.xlsx
+++ b/artfynd/A 50854-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50854-2022 artfynd.xlsx
+++ b/artfynd/A 50854-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92664913</v>
+        <v>104731588</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,26 +708,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fiskebyn, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723116.893596556</v>
+        <v>723138</v>
       </c>
       <c r="R2" t="n">
-        <v>6641136.125346412</v>
+        <v>6641206</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,27 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-04-10</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-04-10</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Eldplats badstigen</t>
+          <t>Letade mat i en död gran just SV badet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,27 +787,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Öström</t>
+          <t>Staffan P Öström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Öström</t>
+          <t>Staffan P Öström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92664915</v>
+        <v>92664911</v>
       </c>
       <c r="B3" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723062.8129469338</v>
+        <v>723138</v>
       </c>
       <c r="R3" t="n">
-        <v>6641171.152372222</v>
+        <v>6641206</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -910,7 +898,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ö 192</t>
+          <t>S Badet</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,12 +913,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Staffan Öström</t>
+          <t>Staffan P Öström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Staffan Öström</t>
+          <t>Staffan P Öström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -940,12 +928,7 @@
         <v>92664912</v>
       </c>
       <c r="B4" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>723133.9461873609</v>
+        <v>723134</v>
       </c>
       <c r="R4" t="n">
-        <v>6641146.219255084</v>
+        <v>6641146</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1056,27 +1039,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Staffan Öström</t>
+          <t>Staffan P Öström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Staffan Öström</t>
+          <t>Staffan P Öström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>92664916</v>
+        <v>92664913</v>
       </c>
       <c r="B5" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,10 +1100,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>723157.7652571864</v>
+        <v>723117</v>
       </c>
       <c r="R5" t="n">
-        <v>6641161.254252221</v>
+        <v>6641136</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1172,7 +1150,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ö Fotbollsplan</t>
+          <t>Eldplats badstigen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1187,15 +1165,897 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Staffan Öström</t>
+          <t>Staffan P Öström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Staffan Öström</t>
+          <t>Staffan P Öström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>92664914</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fiskebyn, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>723057</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6641168</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vätö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>N 199</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>92664915</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fiskebyn, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>723063</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6641171</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vätö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ö 192</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>92664916</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fiskebyn, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>723158</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6641161</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vätö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ö Fotbollsplan</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>92664917</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Fiskebyn, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>723132</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6641054</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vätö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på Ö gräns</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>92664918</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Fiskebyn, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>723112</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6641034</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vätö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>på Ö gräns</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>92664919</v>
+      </c>
+      <c r="B11" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fiskebyn, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>723078</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6640993</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vätö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på Ö gräns</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>92664920</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fiskebyn, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>723019</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6641064</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vätö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-04-10</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>S 176</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Staffan P Öström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50854-2022 artfynd.xlsx
+++ b/artfynd/A 50854-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104731588</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92664911</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,6 +1063,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92664912</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1174,6 +1194,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92664913</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1300,6 +1325,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92664914</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1426,6 +1456,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92664915</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1552,6 +1587,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92664916</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1678,6 +1718,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92664917</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1804,6 +1849,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92664918</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1930,6 +1980,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92664919</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2056,8 +2111,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92664920</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>